--- a/docs/apmi_pms_data.xlsx
+++ b/docs/apmi_pms_data.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All strategies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest month" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All strategies'!$A$1:$R$1225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest month'!$A$1:$R$1225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
